--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1469,7 +1469,7 @@
         <v>10001</v>
       </c>
       <c r="G18" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>18</v>
@@ -1493,7 +1493,7 @@
         <v>10001</v>
       </c>
       <c r="G19" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>19</v>
@@ -1517,7 +1517,7 @@
         <v>10001</v>
       </c>
       <c r="G20" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>20</v>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -53,6 +53,9 @@
     <t>AttrRate</t>
   </si>
   <si>
+    <t>RuneCount</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -93,6 +96,15 @@
   </si>
   <si>
     <t>2002,2003,2005,2007,2010,3008,1004,1005</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>1002,1004,1005</t>
+  </si>
+  <si>
+    <t>2002,2003,2005,2007,2010,3008,1012,2012</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1103,13 +1115,15 @@
       <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1129,33 +1143,37 @@
       <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
@@ -1165,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1174,12 +1192,14 @@
         <v>1000</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
       </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
@@ -1189,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1198,12 +1218,14 @@
         <v>1000</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="4">
         <v>2</v>
       </c>
-      <c r="J7" s="5"/>
+      <c r="J7" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
@@ -1213,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1222,12 +1244,14 @@
         <v>1000</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="4">
         <v>3</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
@@ -1237,22 +1261,24 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" ref="F9:F20" si="0">G6+1</f>
+        <f t="shared" ref="F9:F23" si="0">G6+1</f>
         <v>1001</v>
       </c>
       <c r="G9" s="1">
         <v>2000</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
@@ -1262,7 +1288,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
@@ -1272,12 +1298,14 @@
         <v>2000</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="4">
         <v>2</v>
       </c>
-      <c r="J10" s="5"/>
+      <c r="J10" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
@@ -1287,7 +1315,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
@@ -1297,12 +1325,14 @@
         <v>2000</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="4">
         <v>3</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
@@ -1312,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="0"/>
@@ -1322,12 +1352,14 @@
         <v>5000</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
-      <c r="J12" s="5"/>
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
@@ -1337,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" si="0"/>
@@ -1347,12 +1379,14 @@
         <v>5000</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="4">
         <v>2</v>
       </c>
-      <c r="J13" s="5"/>
+      <c r="J13" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
@@ -1362,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="0"/>
@@ -1372,12 +1406,14 @@
         <v>5000</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="4">
         <v>3</v>
       </c>
-      <c r="J14" s="5"/>
+      <c r="J14" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
@@ -1387,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="0"/>
@@ -1397,12 +1433,14 @@
         <v>10000</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
       </c>
-      <c r="J15" s="5"/>
+      <c r="J15" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
@@ -1412,7 +1450,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="0"/>
@@ -1422,12 +1460,14 @@
         <v>10000</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
@@ -1437,7 +1477,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="0"/>
@@ -1447,14 +1487,16 @@
         <v>10000</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="4">
         <v>3</v>
       </c>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:9">
+      <c r="J17" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1462,23 +1504,26 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
       <c r="G18" s="1">
-        <v>200000</v>
+        <v>45000</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:9">
+      <c r="J18" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1486,23 +1531,26 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
       <c r="G19" s="1">
-        <v>200000</v>
+        <v>45000</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I19" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:9">
+      <c r="J19" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1510,25 +1558,109 @@
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
       <c r="G20" s="1">
-        <v>200000</v>
+        <v>45000</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="4">
         <v>3</v>
       </c>
+      <c r="J20" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="0"/>
+        <v>45001</v>
+      </c>
+      <c r="G21" s="1">
+        <v>200000</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="0"/>
+        <v>45001</v>
+      </c>
+      <c r="G22" s="1">
+        <v>200000</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="0"/>
+        <v>45001</v>
+      </c>
+      <c r="G23" s="1">
+        <v>200000</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="4">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:J5 J3:J4 C3:I4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
